--- a/pokedex_datos.xlsx
+++ b/pokedex_datos.xlsx
@@ -33,18 +33,12 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-        <bgColor rgb="00FFFF00"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -59,11 +53,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,11 +464,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Raichu</t>
+          <t>Pikachu</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -484,19 +477,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E2" t="n">
-        <v>485</v>
+        <v>320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>04/03/2026 09:57</t>
+          <t>05/03/2026 10:56</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Evolucionado</t>
+          <t>Registrado</t>
         </is>
       </c>
     </row>
@@ -522,43 +515,260 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>04/03/2026 09:57</t>
+          <t>05/03/2026 10:56</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Registrado</t>
+          <t>Evolucionado</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Snorlax</t>
+          <t>Pichu</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" t="n">
+        <v>205</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>05/03/2026 11:00</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Pikachu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>35</v>
+      </c>
+      <c r="E5" t="n">
+        <v>320</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>05/03/2026 11:00</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Evolucionado</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Squirtle</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>44</v>
+      </c>
+      <c r="E6" t="n">
+        <v>314</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>05/03/2026 11:06</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Wartortle</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>59</v>
+      </c>
+      <c r="E7" t="n">
+        <v>405</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>05/03/2026 11:06</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Evolucionado</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Wartortle</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>59</v>
+      </c>
+      <c r="E8" t="n">
+        <v>405</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>05/03/2026 11:06</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Evolucionado</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Wartortle</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>59</v>
+      </c>
+      <c r="E9" t="n">
+        <v>405</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>05/03/2026 11:07</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Registrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Blastoise</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>79</v>
+      </c>
+      <c r="E10" t="n">
+        <v>530</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>05/03/2026 11:07</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Evolucionado</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Ditto</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>160</v>
-      </c>
-      <c r="E4" t="n">
-        <v>540</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>04/03/2026 09:57</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>GANADOR</t>
+      <c r="D11" t="n">
+        <v>48</v>
+      </c>
+      <c r="E11" t="n">
+        <v>288</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>05/03/2026 11:14</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Registrado</t>
         </is>
       </c>
     </row>
@@ -567,6 +777,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
